--- a/docs/enterprise/FEATURES.xlsx
+++ b/docs/enterprise/FEATURES.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="372">
   <si>
     <t xml:space="preserve">TenderOS Enterprise: features list</t>
   </si>
@@ -871,6 +871,18 @@
     <t xml:space="preserve">E-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Feedback and change requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give feedback: click any section of any page and write what should change; the Change requests tab lists every request (when, where, comment, by which team) with approve / reject; the approved ones export as one Markdown prompt for jouleWise to apply with Claude Code under the AMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">web/src/feedback; tests/e2e/test_feedback.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Evidence status on every box</t>
   </si>
   <si>
@@ -880,7 +892,7 @@
     <t xml:space="preserve">Faint / with count / signed off at this value / signed at an older value; the register as CSV</t>
   </si>
   <si>
-    <t xml:space="preserve">E-03</t>
+    <t xml:space="preserve">E-04</t>
   </si>
   <si>
     <t xml:space="preserve">Assignments</t>
@@ -889,7 +901,7 @@
     <t xml:space="preserve">A data point assigned to a team or person; answer with a value, note or file; accept or return into the bid as a new version</t>
   </si>
   <si>
-    <t xml:space="preserve">E-04</t>
+    <t xml:space="preserve">E-05</t>
   </si>
   <si>
     <t xml:space="preserve">Pings from any box (@mentions)</t>
@@ -898,7 +910,7 @@
     <t xml:space="preserve">A thread on every input box; mention a teammate; reply with a value; Fill in</t>
   </si>
   <si>
-    <t xml:space="preserve">E-05</t>
+    <t xml:space="preserve">E-06</t>
   </si>
   <si>
     <t xml:space="preserve">Team setup</t>
@@ -907,7 +919,7 @@
     <t xml:space="preserve">People, teams, super admin, titles, the tabs they cover</t>
   </si>
   <si>
-    <t xml:space="preserve">E-06</t>
+    <t xml:space="preserve">E-07</t>
   </si>
   <si>
     <t xml:space="preserve">Activity and audit log</t>
@@ -919,7 +931,7 @@
     <t xml:space="preserve">Activity log today; export to build</t>
   </si>
   <si>
-    <t xml:space="preserve">E-07</t>
+    <t xml:space="preserve">E-08</t>
   </si>
   <si>
     <t xml:space="preserve">Email notifications</t>
@@ -1375,8 +1387,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Features" displayName="Features" ref="A1:I79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Features" displayName="Features" ref="A1:I80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I80"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -1748,7 +1760,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3594,7 +3606,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
         <v>281</v>
       </c>
@@ -3648,20 +3660,22 @@
       <c r="H67" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>277</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>70</v>
@@ -3679,19 +3693,19 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>277</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>109</v>
@@ -3706,32 +3720,30 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>277</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>297</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
@@ -3747,25 +3759,27 @@
         <v>300</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I71" s="4"/>
+      <c r="I71" s="4" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>303</v>
@@ -3774,16 +3788,16 @@
         <v>304</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I72" s="4"/>
     </row>
@@ -3792,40 +3806,40 @@
         <v>305</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>102</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>102</v>
@@ -3834,21 +3848,19 @@
         <v>109</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>311</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
         <v>312</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>313</v>
@@ -3872,12 +3884,12 @@
         <v>315</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
         <v>316</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>317</v>
@@ -3906,7 +3918,7 @@
         <v>320</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>321</v>
@@ -3918,7 +3930,7 @@
         <v>102</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>36</v>
@@ -3926,23 +3938,25 @@
       <c r="H77" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I77" s="4"/>
+      <c r="I77" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>103</v>
@@ -3951,28 +3965,28 @@
         <v>36</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="I78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>36</v>
@@ -3980,8 +3994,35 @@
       <c r="H79" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I79" s="4" t="s">
-        <v>329</v>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -4012,7 +4053,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4029,7 +4070,7 @@
         <v>97</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4037,15 +4078,15 @@
         <v>31</v>
       </c>
       <c r="B3" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A3,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A3,Features!$G$2:$G$80,B$2)</f>
         <v>13</v>
       </c>
       <c r="C3" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A3,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A3,Features!$G$2:$G$80,C$2)</f>
         <v>2</v>
       </c>
       <c r="D3" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A3,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A3,Features!$G$2:$G$80,D$2)</f>
         <v>2</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -4058,15 +4099,15 @@
         <v>106</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A4,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A4,Features!$G$2:$G$80,B$2)</f>
         <v>8</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A4,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A4,Features!$G$2:$G$80,C$2)</f>
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A4,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A4,Features!$G$2:$G$80,D$2)</f>
         <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
@@ -4079,15 +4120,15 @@
         <v>142</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A5,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A5,Features!$G$2:$G$80,B$2)</f>
         <v>12</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A5,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A5,Features!$G$2:$G$80,C$2)</f>
         <v>0</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A5,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A5,Features!$G$2:$G$80,D$2)</f>
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -4100,15 +4141,15 @@
         <v>184</v>
       </c>
       <c r="B6" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A6,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A6,Features!$G$2:$G$80,B$2)</f>
         <v>6</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A6,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A6,Features!$G$2:$G$80,C$2)</f>
         <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A6,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A6,Features!$G$2:$G$80,D$2)</f>
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -4121,15 +4162,15 @@
         <v>87</v>
       </c>
       <c r="B7" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A7,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A7,Features!$G$2:$G$80,B$2)</f>
         <v>15</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A7,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A7,Features!$G$2:$G$80,C$2)</f>
         <v>0</v>
       </c>
       <c r="D7" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A7,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A7,Features!$G$2:$G$80,D$2)</f>
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -4142,15 +4183,15 @@
         <v>260</v>
       </c>
       <c r="B8" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A8,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A8,Features!$G$2:$G$80,B$2)</f>
         <v>3</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A8,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A8,Features!$G$2:$G$80,C$2)</f>
         <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A8,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A8,Features!$G$2:$G$80,D$2)</f>
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -4163,36 +4204,36 @@
         <v>277</v>
       </c>
       <c r="B9" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A9,Features!$G$2:$G$79,B$2)</f>
-        <v>6</v>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A9,Features!$G$2:$G$80,B$2)</f>
+        <v>7</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A9,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A9,Features!$G$2:$G$80,C$2)</f>
         <v>1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A9,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A9,Features!$G$2:$G$80,D$2)</f>
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">SUM(B9:D9)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B10" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A10,Features!$G$2:$G$79,B$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A10,Features!$G$2:$G$80,B$2)</f>
         <v>7</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A10,Features!$G$2:$G$79,C$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A10,Features!$G$2:$G$80,C$2)</f>
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$B$2:$B$79,$A10,Features!$G$2:$G$79,D$2)</f>
+        <f aca="false">COUNTIFS(Features!$B$2:$B$80,$A10,Features!$G$2:$G$80,D$2)</f>
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -4202,11 +4243,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B3:B10)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C3:C10)</f>
@@ -4218,7 +4259,7 @@
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E3:E10)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4230,7 +4271,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4251,7 +4292,7 @@
         <v>97</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4259,20 +4300,20 @@
         <v>37</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A15,Features!$G$2:$G$79,B$14)</f>
-        <v>59</v>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A15,Features!$G$2:$G$80,B$14)</f>
+        <v>60</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A15,Features!$G$2:$G$79,C$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A15,Features!$G$2:$G$80,C$14)</f>
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A15,Features!$G$2:$G$79,D$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A15,Features!$G$2:$G$80,D$14)</f>
         <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">SUM(B15:D15)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4280,15 +4321,15 @@
         <v>53</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A16,Features!$G$2:$G$79,B$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A16,Features!$G$2:$G$80,B$14)</f>
         <v>7</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A16,Features!$G$2:$G$79,C$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A16,Features!$G$2:$G$80,C$14)</f>
         <v>3</v>
       </c>
       <c r="D16" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A16,Features!$G$2:$G$79,D$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A16,Features!$G$2:$G$80,D$14)</f>
         <v>2</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -4301,15 +4342,15 @@
         <v>88</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A17,Features!$G$2:$G$79,B$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A17,Features!$G$2:$G$80,B$14)</f>
         <v>4</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A17,Features!$G$2:$G$79,C$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A17,Features!$G$2:$G$80,C$14)</f>
         <v>1</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$H$2:$H$79,$A17,Features!$G$2:$G$79,D$14)</f>
+        <f aca="false">COUNTIFS(Features!$H$2:$H$80,$A17,Features!$G$2:$G$80,D$14)</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
@@ -4326,7 +4367,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -4344,7 +4385,7 @@
         <v>97</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E20" s="7"/>
     </row>
@@ -4353,11 +4394,11 @@
         <v>118</v>
       </c>
       <c r="B21" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A21,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A21,Features!$G$2:$G$80,"Extend")</f>
         <v>0</v>
       </c>
       <c r="C21" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A21,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A21,Features!$G$2:$G$80,"Build")</f>
         <v>0</v>
       </c>
       <c r="D21" s="7" t="n">
@@ -4371,11 +4412,11 @@
         <v>142</v>
       </c>
       <c r="B22" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A22,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A22,Features!$G$2:$G$80,"Extend")</f>
         <v>0</v>
       </c>
       <c r="C22" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A22,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A22,Features!$G$2:$G$80,"Build")</f>
         <v>0</v>
       </c>
       <c r="D22" s="7" t="n">
@@ -4389,11 +4430,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A23,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A23,Features!$G$2:$G$80,"Extend")</f>
         <v>0</v>
       </c>
       <c r="C23" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A23,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A23,Features!$G$2:$G$80,"Build")</f>
         <v>0</v>
       </c>
       <c r="D23" s="7" t="n">
@@ -4407,11 +4448,11 @@
         <v>34</v>
       </c>
       <c r="B24" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A24,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A24,Features!$G$2:$G$80,"Extend")</f>
         <v>0</v>
       </c>
       <c r="C24" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A24,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A24,Features!$G$2:$G$80,"Build")</f>
         <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
@@ -4425,11 +4466,11 @@
         <v>129</v>
       </c>
       <c r="B25" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A25,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A25,Features!$G$2:$G$80,"Extend")</f>
         <v>0</v>
       </c>
       <c r="C25" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A25,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A25,Features!$G$2:$G$80,"Build")</f>
         <v>1</v>
       </c>
       <c r="D25" s="7" t="n">
@@ -4443,11 +4484,11 @@
         <v>102</v>
       </c>
       <c r="B26" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A26,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A26,Features!$G$2:$G$80,"Extend")</f>
         <v>1</v>
       </c>
       <c r="C26" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A26,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A26,Features!$G$2:$G$80,"Build")</f>
         <v>2</v>
       </c>
       <c r="D26" s="7" t="n">
@@ -4461,11 +4502,11 @@
         <v>70</v>
       </c>
       <c r="B27" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A27,Features!$G$2:$G$79,"Extend")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A27,Features!$G$2:$G$80,"Extend")</f>
         <v>3</v>
       </c>
       <c r="C27" s="7" t="n">
-        <f aca="false">COUNTIFS(Features!$E$2:$E$79,$A27,Features!$G$2:$G$79,"Build")</f>
+        <f aca="false">COUNTIFS(Features!$E$2:$E$80,$A27,Features!$G$2:$G$80,"Build")</f>
         <v>0</v>
       </c>
       <c r="D27" s="7" t="n">
@@ -4501,156 +4542,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>118</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>87</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
